--- a/data.xlsx
+++ b/data.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="F:\小P主硬碟\2026_SunForce_Asset_Query_System\sunforce-asset-query\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{08481118-D20E-4BE7-B20A-63FA517F8CC6}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{18525B1F-0F68-4D6B-B9BC-3980B8EE5CF5}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="20640" windowHeight="11760" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -3063,7 +3063,7 @@
         <v>72</v>
       </c>
       <c r="D2" s="6">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="E2" s="7" t="s">
         <v>0</v>

--- a/data.xlsx
+++ b/data.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="F:\小P主硬碟\2026_SunForce_Asset_Query_System\sunforce-asset-query\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{18525B1F-0F68-4D6B-B9BC-3980B8EE5CF5}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{08C017F0-30AE-4C15-9CCD-86C068A86A11}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="20640" windowHeight="11760" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -3063,7 +3063,7 @@
         <v>72</v>
       </c>
       <c r="D2" s="6">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="E2" s="7" t="s">
         <v>0</v>
